--- a/inst/testdata/registryid/testinput_registry_id_8.xlsx
+++ b/inst/testdata/registryid/testinput_registry_id_8.xlsx
@@ -20,52 +20,52 @@
     <t xml:space="preserve">PRIMARY_NAME</t>
   </si>
   <si>
-    <t xml:space="preserve">110071293460</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EJAM INC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">110070874073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EJAM INC.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">110070538057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BEJAMIN HAFERTEPE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">110044340807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NEJAME &amp; SONS INC.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">110030509215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KREJAM CORP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">110019033810</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HEJAMADA CAMPGROUND &amp; RV PARK</t>
-  </si>
-  <si>
-    <t xml:space="preserve">110056111559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LA VEJAMA DISCOUNT STORE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">110056982323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GRACEJAMES ENT, LLC</t>
+    <t xml:space="preserve">110040017335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FORT FREDERICK STATE PARK - PICNIC AREA-WTP - PICNIC AREA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">110030524742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PRESTIGE LEXUS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">110070429577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OAKS CENTER OIL INC DBA OAKS SHELL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">110070559520</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HOUSTON COUNTY HHW PROGRAM EVENT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">110005007759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CRASH CHAMPIONS, LLC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">110022900958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TWIN RIVERS PLATING</t>
+  </si>
+  <si>
+    <t xml:space="preserve">110063586294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">US POSTAL SVC LANGHORNE FAC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">110072073968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MOUNTAIN SHADOWS APARTMENTS</t>
   </si>
 </sst>
 </file>
